--- a/ROCm_Defect_Dashboard.xlsx
+++ b/ROCm_Defect_Dashboard.xlsx
@@ -2162,7 +2162,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ROCm  Defect Dashboard</t>
+          <t>App  Defect Dashboard</t>
         </is>
       </c>
     </row>
